--- a/output/2026-09-05_00_Italia_Calabria_Impiantistica_aspirazione_industriale.xlsx
+++ b/output/2026-09-05_00_Italia_Calabria_Impiantistica_aspirazione_industriale.xlsx
@@ -484,7 +484,6 @@
           <t>0984 38270</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>Attiva dal 1971, Rende (CS), Contrada Lecco Zona Industriale. Esistenza e attivita' confermate via ricerca web (amministrazionicomunali.it, reportaziende.it, sito aziendale). Linea prodotti aspirazione/aspiratori industriali confermata.</t>
@@ -522,10 +521,9 @@
           <t>0984 461129</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Attiva dal 1975, Castrolibero (CS), Via Pirelli 10 (fatturato 2022 ca. 6,9 mln euro, 20-49 dipendenti). Esistenza confermata via ricerca web. Offerta aspiratori fumi saldatura coerente col profilo aziendale (gas tecnici/saldatura); pagina prodotto specifica non reperita direttamente per conferma puntuale.</t>
+          <t>Attiva dal 1975, Castrolibero (CS), Via Pirelli 10 (fatturato 2022 ca. 6,9 mln euro, 20-49 dipendenti). Esistenza confermata via ricerca web. Offerta aspiratori fumi saldatura coerente col profilo aziendale (gas tecnici/saldatura); pagina prodotto specifica non reperita direttamente per conferma puntuale. [DUPLICATO — vedi anche: 2026-09-05_00_Italia_Calabria_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -597,8 +595,6 @@
           <t>Vendita sistemi aspirapolvere centralizzato domestico Aertecnica Tubò</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>SCARTATO: prodotto e' aspirapolvere centralizzato AD USO DOMESTICO (non impiantistica aspirazione industriale); attivita' principale dell'azienda e' automazione cancelli/sicurezza. Fuori target settore.</t>
@@ -616,7 +612,6 @@
           <t>Anacoreta Alfonso (Ferramenta/Macchine utensili)</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>Cosenza</t>
@@ -627,8 +622,6 @@
           <t>Ferramenta al dettaglio e lavorazione ferro battuto (cancelli, inferriate, ringhiere)</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>SCARTATO: verifica web mostra attivita' reale = ferramenta al dettaglio e lavorazione ferro battuto (ATECO 47.52.1), nessuna evidenza di macchine per legno/metallo/PVC o impianti di aspirazione trucioli come da descrizione grezza. Descrizione non coerente con riscontri reali.</t>
@@ -646,7 +639,6 @@
           <t>Cria SM S.r.l.</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>Cosenza</t>
@@ -657,8 +649,6 @@
           <t>Ricambi e attrezzature per settore agricolo e industriale generico</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>SCARTATO: fornitore di ricambi/attrezzature per macchine agricole, movimento terra, lubrificanti e antinfortunistica; nessuna evidenza di offerta impiantistica aspirazione industriale.</t>
@@ -691,8 +681,6 @@
           <t>Impianti elettrici civili e industriali, climatizzazione, domotica, fotovoltaico, cancelli</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>SCARTATO: attivita' confermata = impianti elettrici/climatizzazione/domotica generici; nessuna evidenza di offerta aspirazione industriale.</t>
@@ -730,7 +718,6 @@
           <t>0961 771123</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
           <t>SCARTATO: centro assistenza Aermec per refrigerazione/climatizzazione civile-commerciale-industriale generica; nessuna evidenza di offerta aspirazione industriale.</t>
@@ -768,7 +755,6 @@
           <t>0961 744655</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
           <t>SCARTATO: impiantista termoidraulico/climatizzazione/antincendio generico da 50 anni; nessuna evidenza di offerta aspirazione industriale specifica (dust/fumi).</t>
@@ -843,8 +829,6 @@
           <t>Impianti tecnologici civili e industriali (elettrico, climatizzazione, fotovoltaico, allarmi, ristrutturazioni)</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
           <t>SCARTATO: impiantista tecnologico generico multi-servizio (elettrico/climatizzazione/fotovoltaico/allarmi); nessuna evidenza di offerta aspirazione industriale.</t>
@@ -1114,7 +1098,6 @@
           <t>Ramit S.r.l.</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
           <t>Crotone</t>
@@ -1130,7 +1113,6 @@
           <t>0962 902338</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
           <t>SCARTATO: distributore di articoli tecnici industriali generici (ATECO 51); indirizzo discordante tra fonti (Via Pignataro 18 / Via Nicoletta Mario 147); nessuna evidenza di offerta aspirazione industriale.</t>
@@ -1148,7 +1130,6 @@
           <t>La Costanzo Impianti</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
           <t>Crotone</t>
@@ -1159,8 +1140,6 @@
           <t>Impianti civili e industriali termoidraulici, climatizzazione, antincendio, solare termico</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
           <t>SCARTATO: impiantista termoidraulico/climatizzazione/antincendio/solare generico; nessun sito web proprio verificabile; nessuna evidenza di offerta aspirazione industriale.</t>
@@ -1282,7 +1261,6 @@
           <t>+39 393 9119151</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
           <t>SCARTATO: impiantista termoidraulico generico; nessuna evidenza di offerta aspirazione industriale.</t>
@@ -1300,7 +1278,6 @@
           <t>Idrocliama impianti di Antonio Mancuso</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr">
         <is>
           <t>Vibo Valentia</t>
@@ -1311,8 +1288,6 @@
           <t>Idraulica e termoidraulica civile/industriale</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
           <t>SCARTATO: idraulico/termoidraulico generico (localita' Filandari, VV); nessun sito web verificabile; nessuna evidenza di offerta aspirazione industriale.</t>
@@ -1330,7 +1305,6 @@
           <t>G&amp;G Components Srl</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr">
         <is>
           <t>Vibo Valentia</t>
@@ -1341,8 +1315,6 @@
           <t>Produzione cappe aspiranti da cucina in acciaio inox (elettrodomestici, uso domestico/ristorazione)</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
           <t>SCARTATO: azienda MANIFATTURIERA/PRODUTTRICE di cappe aspiranti per cucina ad uso domestico/ristorazione; ambito domestico non industriale, si tratta di un produttore/utilizzatore finale del prodotto e non di un distributore di impiantistica aspirazione industriale.</t>
